--- a/know-all/outputs/20260324_鸡尾酒/01_审核稿.xlsx
+++ b/know-all/outputs/20260324_鸡尾酒/01_审核稿.xlsx
@@ -39,6 +39,7 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
+      <color rgb="00222222"/>
       <sz val="11"/>
     </font>
   </fonts>
@@ -72,20 +73,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -456,13 +456,13 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="52" customWidth="1" min="5" max="5"/>
-    <col width="52" customWidth="1" min="6" max="6"/>
-    <col width="52" customWidth="1" min="7" max="7"/>
-    <col width="52" customWidth="1" min="8" max="8"/>
+    <col width="54" customWidth="1" min="5" max="5"/>
+    <col width="54" customWidth="1" min="6" max="6"/>
+    <col width="54" customWidth="1" min="7" max="7"/>
+    <col width="54" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -471,45 +471,40 @@
           <t>专题信息</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+    </row>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>专题</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>鸡尾酒</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="24" customHeight="1">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>专题</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>鸡尾酒</t>
-        </is>
-      </c>
-    </row>
     <row r="3" ht="24" customHeight="1">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>状态</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>待人工确认</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="24" customHeight="1">
-      <c r="A4" t="inlineStr">
+    <row r="4" ht="42" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>这份本地表格是当前审核阶段唯一 source of truth。</t>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>本地审核表格是审核阶段唯一 source of truth。只有在用户明确确认后，才允许进入出图。</t>
         </is>
       </c>
     </row>
@@ -520,7 +515,7 @@
           <t>标题</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>鸡尾酒这5件事别想当然🍸</t>
         </is>
@@ -535,24 +530,24 @@
       </c>
     </row>
     <row r="9" ht="24" customHeight="1">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>主标题</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>很多人喝鸡尾酒，但没真搞懂鸡尾酒</t>
         </is>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>副标题</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>从甜度到冰块，这几件事最容易想当然</t>
         </is>
@@ -560,454 +555,448 @@
     </row>
     <row r="11" ht="24" customHeight="1"/>
     <row r="12" ht="24" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>封面列点</t>
         </is>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>序号</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>mark_raw</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>mark_render</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>文本</t>
         </is>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>🍸</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>甜</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>甜不等于度数低</t>
         </is>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>02</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>🧊</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>冰</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>冰块不只是降温</t>
         </is>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>03</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>🥄</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>摇</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>摇和搅不是随便选</t>
         </is>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>04</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>🍊</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>装</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>装饰物不只是好看</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="78" customHeight="1">
-      <c r="A18" t="inlineStr">
+    <row r="18" ht="24" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>05</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>📏</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>长</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t>长饮短饮不是分量区别</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="78" customHeight="1"/>
-    <row r="20" ht="78" customHeight="1">
+    <row r="19" ht="24" customHeight="1"/>
+    <row r="20" ht="24" customHeight="1">
       <c r="A20" s="1" t="inlineStr">
         <is>
           <t>知识卡</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="78" customHeight="1">
-      <c r="A21" s="4" t="inlineStr">
+    <row r="21" ht="24" customHeight="1"/>
+    <row r="22" ht="24" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>卡片ID</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>标题</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>mark_raw</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D22" s="4" t="inlineStr">
         <is>
           <t>mark_render</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
+      <c r="E22" s="4" t="inlineStr">
         <is>
           <t>正文1</t>
         </is>
       </c>
-      <c r="F21" s="4" t="inlineStr">
+      <c r="F22" s="4" t="inlineStr">
         <is>
           <t>正文2</t>
         </is>
       </c>
-      <c r="G21" s="4" t="inlineStr">
+      <c r="G22" s="4" t="inlineStr">
         <is>
           <t>正文3</t>
         </is>
       </c>
-      <c r="H21" s="4" t="inlineStr">
+      <c r="H22" s="4" t="inlineStr">
         <is>
           <t>正文4</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="78" customHeight="1">
-      <c r="A22" s="5" t="inlineStr">
+    <row r="23" ht="92" customHeight="1">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>甜不等于度数低 🍸</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
+      <c r="C23" s="3" t="inlineStr">
         <is>
           <t>🍸</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="D23" s="3" t="inlineStr">
         <is>
           <t>甜</t>
         </is>
       </c>
-      <c r="E22" s="5" t="inlineStr">
+      <c r="E23" s="3" t="inlineStr">
         <is>
           <t>很多人第一次喝鸡尾酒，尤其是果味重、入口顺的那种，很容易马上给它下一个判断：这杯应该度数不高。这个印象特别常见，因为人对“烈”的判断，往往先靠舌头感受到的冲不冲，而不是看配方里到底放了多少酒。</t>
         </is>
       </c>
-      <c r="F22" s="5" t="inlineStr">
+      <c r="F23" s="3" t="inlineStr">
         <is>
           <t>但鸡尾酒甜不甜，和它酒精度高不高，根本不是同一个维度。糖浆、利口酒、果汁、汽水都能把辛辣感压下去，让酒喝起来更顺，所以有些酒入口像饮料，后劲却一点都不轻。尤其是一些以朗姆、伏特加、龙舌兰为底的调法，表面好入口，不代表底酒放得少。</t>
         </is>
       </c>
-      <c r="G22" s="5" t="inlineStr">
+      <c r="G23" s="3" t="inlineStr">
         <is>
           <t>所以鸡尾酒“好喝、甜、顺”很多时候只是风味设计做得好，不等于它温柔。真想判断它顶不顶，得看基酒种类、配方比例和一杯里到底放了几份酒，而不是只看它像不像果汁。</t>
         </is>
       </c>
-      <c r="H22" s="5" t="n"/>
-    </row>
-    <row r="23" ht="78" customHeight="1">
-      <c r="A23" s="5" t="inlineStr">
+      <c r="H23" s="3" t="n"/>
+    </row>
+    <row r="24" ht="92" customHeight="1">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t>02</t>
         </is>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>冰块不只是降温 🧊</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr">
+      <c r="C24" s="3" t="inlineStr">
         <is>
           <t>🧊</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="D24" s="3" t="inlineStr">
         <is>
           <t>冰</t>
         </is>
       </c>
-      <c r="E23" s="5" t="inlineStr">
+      <c r="E24" s="3" t="inlineStr">
         <is>
           <t>很多人看调酒时会觉得冰块这东西挺工具化的，好像只是把酒弄凉一点，夏天喝起来更舒服。于是有人会随手少放冰，觉得这样更“实在”，甚至以为冰放多了只是店家在省酒。</t>
         </is>
       </c>
-      <c r="F23" s="5" t="inlineStr">
+      <c r="F24" s="3" t="inlineStr">
         <is>
           <t>但冰块在鸡尾酒里不只是负责冷，它还直接影响稀释速度、香气打开的节奏和整杯酒的口感平衡。冰块大、硬、融得慢，酒会更稳；冰块小、碎、融得快，味道会更快被冲淡。很多经典鸡尾酒之所以对冰型、冰量有讲究，就是因为酒不是一兑完就结束，而是在你喝的那几分钟里持续变化。</t>
         </is>
       </c>
-      <c r="G23" s="5" t="inlineStr">
+      <c r="G24" s="3" t="inlineStr">
         <is>
           <t>也就是说，冰不是附属品，而是配方的一部分。少冰未必更赚，很多时候反而会让一杯本来该干净利落的酒变得又温又散。</t>
         </is>
       </c>
-      <c r="H23" s="5" t="n"/>
-    </row>
-    <row r="24" ht="78" customHeight="1">
-      <c r="A24" s="5" t="inlineStr">
+      <c r="H24" s="3" t="n"/>
+    </row>
+    <row r="25" ht="92" customHeight="1">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t>03</t>
         </is>
       </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="B25" s="3" t="inlineStr">
         <is>
           <t>摇和搅不是随便选 🥄</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
+      <c r="C25" s="3" t="inlineStr">
         <is>
           <t>🥄</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="D25" s="3" t="inlineStr">
         <is>
           <t>调</t>
         </is>
       </c>
-      <c r="E24" s="5" t="inlineStr">
+      <c r="E25" s="3" t="inlineStr">
         <is>
           <t>很多人看调酒时会把“摇一摇”和“搅一搅”当成表演差异，觉得哪个更顺手就用哪个，甚至以为大力摇壶只是为了看起来更专业。</t>
         </is>
       </c>
-      <c r="F24" s="5" t="inlineStr">
+      <c r="F25" s="3" t="inlineStr">
         <is>
           <t>其实这两种动作处理的是不同类型的酒。像只含烈酒、追求清澈和顺滑质地的配方，更常用搅拌，因为它能在降温和稀释的同时，尽量保持酒体干净；如果酒里有果汁、蛋清、奶、糖浆这些更容易分层或需要充分融合的材料，就更适合摇和，让液体快速混匀，也顺便打出更饱满的口感。</t>
         </is>
       </c>
-      <c r="G24" s="5" t="inlineStr">
+      <c r="G25" s="3" t="inlineStr">
         <is>
           <t>所以“摇还是搅”不是仪式感，而是针对材料和目标风味做选择。用错了方法，酒未必难喝，但质地、香气和观感通常都会跑偏。</t>
         </is>
       </c>
-      <c r="H24" s="5" t="n"/>
-    </row>
-    <row r="25" ht="78" customHeight="1">
-      <c r="A25" s="5" t="inlineStr">
+      <c r="H25" s="3" t="n"/>
+    </row>
+    <row r="26" ht="92" customHeight="1">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>04</t>
         </is>
       </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="B26" s="3" t="inlineStr">
         <is>
           <t>装饰物不只是好看 🍊</t>
         </is>
       </c>
-      <c r="C25" s="5" t="inlineStr">
+      <c r="C26" s="3" t="inlineStr">
         <is>
           <t>🍊</t>
         </is>
       </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="D26" s="3" t="inlineStr">
         <is>
           <t>饰</t>
         </is>
       </c>
-      <c r="E25" s="5" t="inlineStr">
+      <c r="E26" s="3" t="inlineStr">
         <is>
           <t>很多人看到杯边的橙皮、柠檬片、樱桃、迷迭香，第一反应就是：这不就是为了好看、方便拍照吗？这个想法不奇怪，因为装饰物最先被看到的，确实是视觉效果。</t>
         </is>
       </c>
-      <c r="F25" s="5" t="inlineStr">
+      <c r="F26" s="3" t="inlineStr">
         <is>
           <t>但不少装饰物本来就是风味设计的一部分。比如一条挤过油的橙皮，带来的不只是颜色，而是果皮精油的香气；柠檬皮、薄荷、香草这些东西，会先通过闻香影响你对这杯酒的整体感受。鸡尾酒很多时候不是只靠嘴巴喝，鼻子在前面的判断也很重要，所以装饰并不只是“摆盘”，它常常直接参与了第一口之前的味觉预期。</t>
         </is>
       </c>
-      <c r="G25" s="5" t="inlineStr">
+      <c r="G26" s="3" t="inlineStr">
         <is>
           <t>所以有些装饰你可以拿掉，但拿掉以后，这杯酒给人的完整印象确实会变。它不一定决定酒能不能喝，却经常决定这杯酒像不像原本想做成的样子。</t>
         </is>
       </c>
-      <c r="H25" s="5" t="n"/>
-    </row>
-    <row r="26" ht="78" customHeight="1">
-      <c r="A26" s="5" t="inlineStr">
+      <c r="H26" s="3" t="n"/>
+    </row>
+    <row r="27" ht="92" customHeight="1">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>05</t>
         </is>
       </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>长饮短饮不是分量区别 📏</t>
         </is>
       </c>
-      <c r="C26" s="5" t="inlineStr">
+      <c r="C27" s="3" t="inlineStr">
         <is>
           <t>📏</t>
         </is>
       </c>
-      <c r="D26" s="5" t="inlineStr">
+      <c r="D27" s="3" t="inlineStr">
         <is>
           <t>杯</t>
         </is>
       </c>
-      <c r="E26" s="5" t="inlineStr">
+      <c r="E27" s="3" t="inlineStr">
         <is>
           <t>很多人一听“长饮”“短饮”，会顺手理解成：一个就是大杯慢慢喝，一个就是小杯一口闷。这个理解抓到了一点表面差异，但还不够。</t>
         </is>
       </c>
-      <c r="F26" s="5" t="inlineStr">
+      <c r="F27" s="3" t="inlineStr">
         <is>
           <t>长饮和短饮更核心的区别，不只是杯子大小，而是饮用方式和配方结构。长饮通常会加更多无酒精成分，比如苏打水、汤力水、果汁、碎冰，整体更稀释，也更适合拉长饮用时间；短饮则往往更集中、更利落，强调香气、结构和第一口到收尾的完整感。所以它们不是简单的“大杯和小杯”，而是两种不同的喝法。</t>
         </is>
       </c>
-      <c r="G26" s="5" t="inlineStr">
+      <c r="G27" s="3" t="inlineStr">
         <is>
           <t>也就是说，看到杯子大，不代表这酒就一定更轻；看到杯子小，也不代表它就只剩“猛”。判断鸡尾酒类型，还是得回到它怎么调、怎么喝，而不是只看杯型和容量。</t>
         </is>
       </c>
-      <c r="H26" s="5" t="n"/>
-    </row>
-    <row r="27" ht="78" customHeight="1"/>
-    <row r="28" ht="78" customHeight="1"/>
-    <row r="29" ht="78" customHeight="1"/>
-    <row r="30" ht="78" customHeight="1">
+      <c r="H27" s="3" t="n"/>
+    </row>
+    <row r="28" ht="92" customHeight="1"/>
+    <row r="29" ht="24" customHeight="1"/>
+    <row r="30" ht="24" customHeight="1">
       <c r="A30" s="1" t="inlineStr">
         <is>
           <t>#话题</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="78" customHeight="1">
+    <row r="31" ht="24" customHeight="1">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>话题</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="78" customHeight="1">
-      <c r="A32" t="inlineStr">
-        <is>
           <t>#鸡尾酒知识</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="78" customHeight="1">
-      <c r="A33" t="inlineStr">
+    <row r="32" ht="24" customHeight="1">
+      <c r="A32" s="3" t="inlineStr">
         <is>
           <t>#调酒入门</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="78" customHeight="1">
-      <c r="A34" t="inlineStr">
+    <row r="33" ht="24" customHeight="1">
+      <c r="A33" s="3" t="inlineStr">
         <is>
           <t>#喝酒日常</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="78" customHeight="1">
-      <c r="A35" t="inlineStr">
+    <row r="34" ht="24" customHeight="1">
+      <c r="A34" s="3" t="inlineStr">
         <is>
           <t>#生活常识</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="78" customHeight="1">
-      <c r="A36" t="inlineStr">
+    <row r="35" ht="24" customHeight="1">
+      <c r="A35" s="3" t="inlineStr">
         <is>
           <t>#涨知识</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="78" customHeight="1">
-      <c r="A37" t="inlineStr">
+    <row r="36" ht="24" customHeight="1">
+      <c r="A36" s="3" t="inlineStr">
         <is>
           <t>#每日闲聊语料库</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="78" customHeight="1"/>
-    <row r="39" ht="78" customHeight="1"/>
+    <row r="37" ht="24" customHeight="1"/>
+    <row r="38" ht="24" customHeight="1"/>
+    <row r="39" ht="24" customHeight="1"/>
     <row r="40" ht="48" customHeight="1">
       <c r="A40" s="1" t="inlineStr">
         <is>
           <t>确认说明</t>
         </is>
       </c>
-      <c r="B40" s="5" t="inlineStr">
-        <is>
-          <t>请直接修改这份本地表格。只有在明确说“文稿无误”或“可以出图”后，才允许进入出图阶段。</t>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>请直接修改这份本地审核表格。只有在明确说“文稿无误”或“可以出图”后，才允许进入图片阶段。</t>
         </is>
       </c>
     </row>
